--- a/Tests/excel/module09_test_cases.xlsx
+++ b/Tests/excel/module09_test_cases.xlsx
@@ -1374,17 +1374,17 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng tài khoản Student hợp lệ</t>
+          <t>Log in with a valid Student account</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Xác minh học sinh có email thuộc domain @student.passerellesnumeriques.org đăng nhập thành công vào Student Portal qua Google OAuth.</t>
+          <t>Verify student co email thuoc domain @student.passerellesnumeriques.org log in successfully vao Student Portal qua Google OAuth.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống. Trình duyệt đã kết nối internet và hỗ trợ Google OAuth.</t>
+          <t>Nguoi dung chua log in system. Trinh duyet da ket noi internet va ho tro Google OAuth.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Tại màn hình đăng nhập Google OAuth, nhập tài khoản student01@student.passerellesnumeriques.org.
-3. Nhập mật khẩu hợp lệ và đồng ý cấp quyền nếu có.
-4. Quan sát trang web sau khi chuyển hướng.</t>
+          <t>1. Truy cap URL cua system.
+2. Tai man hinh log in Google OAuth, enter account student01@student.passerellesnumeriques.org.
+3. Enter mat khau hop le va dong y cap quyen neu co.
+4. Observe trang web sau khi redirect.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công. Giao diện tự động chuyển hướng đến Student Portal (mặc định mở tab Academic).
-Thông tin của học sinh hiển thị chính xác bao gồm Họ tên, Mã học sinh ở góc màn hình.
-Dữ liệu điểm học tập của chính học sinh này được tải lên thành công.</t>
+          <t>Log in successfully. Interface tu dong redirect den Student Portal (mac dinh mo tab Academic).
+Thong tin cua student display chinh xac bao gom Ho ten, Ma student o goc man hinh.
+Du lieu grade hoc tap cua chinh student nay duoc tai len successfully.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1420,11 +1420,11 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, M09-F07, Rule 7.1, Rule 7.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+          <t>Related to M09-F01, M09-F07, Rule 7.1, Rule 7.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="105" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>TC-M09-002</t>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng tài khoản Staff của tổ chức</t>
+          <t>Log in with an organization Staff account</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản Staff khi đăng nhập qua Google OAuth sẽ được tự động nhận diện domain và chuyển hướng đến Staff Portal thay vì Student Portal.</t>
+          <t>Verify account Staff khi log in qua Google OAuth se duoc tu dong nhan dien domain va redirect den Staff Portal thay vi Student Portal.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống.</t>
+          <t>Nguoi dung chua log in system.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1467,16 +1467,16 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Thực hiện đăng nhập qua Google OAuth bằng tài khoản staff_user@passerellesnumeriques.org.
-3. Quan sát giao diện sau khi đăng nhập thành công.</t>
+          <t>1. Truy cap URL cua system.
+2. Thuc hien log in qua Google OAuth bang account staff_user@passerellesnumeriques.org.
+3. Observe interface sau khi log in successfully.</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công.
-Hệ thống tự động nhận diện email thuộc domain @passerellesnumeriques.org.
-Chuyển hướng người dùng sang Staff Portal với đầy đủ tính năng quản trị. Không hiển thị giao diện Student Portal.</t>
+          <t>Log in successfully.
+System tu dong nhan dien email thuoc domain @passerellesnumeriques.org.
+Chuyen huong user sang Staff Portal voi day du tinh nang quan tri. Khong display interface Student Portal.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1492,11 +1492,11 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, Rule 7.1, Docs - Mục 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="120" customHeight="1">
+          <t>Related to M09-F01, Rule 7.1, Docs - Section 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="105" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-M09-003</t>
@@ -1519,17 +1519,17 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng tài khoản cá nhân ngoài tổ chức</t>
+          <t>Log in with an external personal account</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản email không thuộc các domain của tổ chức (ví dụ @gmail.com) bị hệ thống chặn truy cập.</t>
+          <t>Verify account email khong thuoc cac domain cua organization (e.g. @gmail.com) bi system chan access.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống.</t>
+          <t>Nguoi dung chua log in system.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1539,16 +1539,16 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Thực hiện đăng nhập qua Google OAuth bằng tài khoản guest_user@gmail.com.
-3. Quan sát phản hồi của hệ thống.</t>
+          <t>1. Truy cap URL cua system.
+2. Thuc hien log in qua Google OAuth bang account guest_user@gmail.com.
+3. Observe phan hoi cua system.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Đăng nhập thất bại.
-Hệ thống từ chối quyền truy cập của email domain @gmail.com.
-Chuyển hướng người dùng sang trang báo lỗi "Access Denied" (Từ chối truy cập). Không tải bất kỳ dữ liệu nào của hệ thống.</t>
+          <t>Log in failed.
+System denies quyen access cua email domain @gmail.com.
+Chuyen huong user sang trang bao error "Access Denied" (Tu choi access). Khong tai bat ky du lieu nao cua system.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, Rule 7.1, Error Handling (Mục 9)</t>
+          <t>Related to M09-F01, Rule 7.1, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng email student hợp lệ nhưng không có dữ liệu trong hệ thống</t>
+          <t>Log in with valid student email but without academic records in system</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không bị lỗi crash và hiển thị thông điệp phù hợp khi email student thuộc domain hợp lệ nhưng không nằm trong danh sách dữ liệu học sinh.</t>
+          <t>Verify system khong bi error crash va display thong diep phu hop khi email student thuoc domain hop le nhung khong nam trong danh sach du lieu student.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập hệ thống. Tài khoản Google student tồn tại nhưng email này chưa được cấu hình trong Sheet danh sách học sinh.</t>
+          <t>Nguoi dung chua log in system. Tai khoan Google student ton tai nhung email nay chua duoc cau hinh trong Sheet danh sach student.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1611,16 +1611,16 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cập URL của hệ thống.
-2. Thực hiện đăng nhập qua Google OAuth bằng tài khoản new_student@student.passerellesnumeriques.org.
-3. Quan sát giao diện sau khi chuyển hướng thành công.</t>
+          <t>1. Truy cap URL cua system.
+2. Thuc hien log in qua Google OAuth bang account new_student@student.passerellesnumeriques.org.
+3. Observe interface sau khi redirect successfully.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công vào Student Portal.
-Hệ thống không bị lỗi crash/trắng màn hình.
-Hiển thị thông báo rõ ràng cho người dùng: "No academic records found." (Không tìm thấy dữ liệu học tập).</t>
+          <t>Log in successfully vao Student Portal.
+System khong bi error crash/trang man hinh.
+Hien thi notification ro rang cho user: "No academic records found." (Khong tim thay du lieu hoc tap).</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F01, M09-F07, Error Handling (Mục 9)</t>
+          <t>Related to M09-F01, M09-F07, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -1663,18 +1663,18 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Chuyển đổi giữa các học kỳ (Semester Selector)</t>
+          <t>Switching between semesters (Semester Selector)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Xác minh tính năng chuyển đổi học kỳ hiển thị đúng dữ liệu điểm của học kỳ được chọn.</t>
+          <t>Verify tinh nang switching semester display dung du lieu grade cua semester duoc select.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công vào Student Portal.
-Học sinh này đã có dữ liệu điểm ở nhiều học kỳ (ví dụ: Học kỳ 1 và Học kỳ 2).</t>
+          <t>Hoc sinh da log in successfully vao Student Portal.
+Hoc sinh nay da co du lieu grade o nhieu semester (e.g.: Semester 1 va Semester 2).</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1684,18 +1684,18 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Tại giao diện Student Portal, định vị bộ chọn học kỳ (Semester Selector).
-2. Nhấp vào danh sách thả xuống và chọn "Semester 2" (Học kỳ 2).
-3. Quan sát danh sách môn học và điểm số hiển thị.
-4. Nhấp chọn lại "Semester 1" (Học kỳ 1).
-5. Quan sát danh sách môn học và điểm số hiển thị.</t>
+          <t>1. Tai interface Student Portal, dinh vi bo select semester (Semester Selector).
+2. Nhap vao danh sach tha xuong va select "Semester 2" (Semester 2).
+3. Observe danh sach course va grades display.
+4. Nhap select lai "Semester 1" (Semester 1).
+5. Observe danh sach course va grades display.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Bảng điểm cập nhật nhanh chóng và chính xác theo học kỳ được chọn.
-Khi chọn "Semester 2", hệ thống chỉ tải các môn học và điểm số thuộc Học kỳ 2.
-Khi chọn "Semester 1", hệ thống chỉ tải các môn học và điểm số thuộc Học kỳ 1.</t>
+          <t>Bang grade cap nhat nhanh chong va chinh xac theo semester duoc select.
+Khi select "Semester 2", system chi tai cac course va grades thuoc Semester 2.
+Khi select "Semester 1", system chi tai cac course va grades thuoc Semester 1.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F02, Rule 7.2</t>
+          <t>Related to M09-F02, Rule 7.2</t>
         </is>
       </c>
     </row>
@@ -1738,18 +1738,18 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra phân nhóm môn học theo danh mục (Subject Categories)</t>
+          <t>Verify categorization course theo category (Subject Categories)</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Xác minh các môn học trong học kỳ hiển thị đúng phân nhóm theo 4 danh mục đào tạo.</t>
+          <t>Verify cac course trong semester display dung categorization theo 4 category dao create.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công vào Student Portal.
-Học kỳ hiện tại có chứa các môn học thuộc cả 4 danh mục.</t>
+          <t>Hoc sinh da log in successfully vao Student Portal.
+Semester hien tai co chua cac course thuoc ca 4 category.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1759,16 +1759,16 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn Học kỳ 1.
-2. Quan sát bố cục hiển thị của danh sách môn học.
-3. Kiểm tra xem các môn học có được xếp dưới các tiêu đề nhóm tương ứng hay không: Fundamental, IT, English, Soft Skills.
-4. Đối chiếu môn học cụ thể (ví dụ môn Math phải thuộc Fundamental, Java thuộc IT).</t>
+          <t>1. Select Semester 1.
+2. Observe bo cuc display cua danh sach course.
+3. Verify whether cac course co duoc xep duoi cac tieu de group tuong ung hay khong: Fundamental, IT, English, Soft Skills.
+4. Doi chieu course cu the (e.g. mon Math phai thuoc Fundamental, Java thuoc IT).</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Các môn học được phân nhóm chính xác và hiển thị dưới các tiêu đề danh mục: Fundamental, IT, English, Soft Skills.
-Bố cục phân nhóm rõ ràng, dễ đọc, không có môn học nào bị xếp sai nhóm hoặc không có nhóm.</t>
+          <t>Cac course duoc categorization chinh xac va display duoi cac tieu de category: Fundamental, IT, English, Soft Skills.
+Bo cuc categorization ro rang, de doc, khong co course nao bi xep sai group hoac khong co group.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F02, Rule 7.3</t>
+          <t>Related to M09-F02, Rule 7.3</t>
         </is>
       </c>
     </row>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra tính năng Chỉ đọc (Read-only) của Student Portal</t>
+          <t>Verify tinh nang Read-only (Read-only) cua Student Portal</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Xác minh học sinh hoàn toàn không có quyền chỉnh sửa điểm số hay thực hiện các tác vụ thay đổi dữ liệu trên giao diện.</t>
+          <t>Verify student hoan toan khong co quyen edit grades hay thuc hien cac tac vu thay doi du lieu tren interface.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công vào Student Portal và đang ở màn hình hiển thị điểm.</t>
+          <t>Hoc sinh da log in successfully vao Student Portal va dang o man hinh display grade.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1831,16 +1831,16 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Quan sát toàn bộ giao diện màn hình Academic.
-2. Kiểm tra sự xuất hiện của các nút: Chỉnh sửa (Edit), Lưu (Save), Xóa (Delete), Nhập điểm (Import), Tải lên (Upload).
-3. Thử nhấp chuột vào các ô điểm số (KT TX, ĐK1-ĐK6, TCK, TLCK, Final Score, GPA).
-4. Thử gõ bàn phím để thay đổi giá trị điểm.</t>
+          <t>1. Observe toan bo interface man hinh Academic.
+2. Verify su xuat hien cua cac nut: Edit (Edit), Save (Save), Delete (Delete), Enter grade (Import), Upload (Upload).
+3. Thu click chuot vao cac o grades (KT TX, DK1-DK6, TCK, TLCK, Final Score, GPA).
+4. Thu go ban phim de thay doi gia tri grade.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Giao diện không hiển thị bất kỳ nút hoặc công cụ nào cho phép chỉnh sửa, lưu, xóa hoặc nhập dữ liệu.
-Tất cả điểm số hiển thị dưới dạng văn bản tĩnh (read-only), không thể nhấp vào để chỉnh sửa hay nhập liệu từ bàn phím.</t>
+          <t>Interface not displayed bat ky nut hoac cong cu nao allows edit, save, delete hoac enter du lieu.
+Tat ca grades display as van ban tinh (read-only), cannot click vao de edit hay enter lieu tu ban phim.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F02, Rule 7.4</t>
+          <t>Related to M09-F02, Rule 7.4</t>
         </is>
       </c>
     </row>
@@ -1883,17 +1883,17 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Hiển thị điểm số chưa được nhập (Empty Grades)</t>
+          <t>Hien thi grades chua duoc enter (Empty Grades)</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Xác minh các ô điểm số chưa có dữ liệu sẽ hiển thị ký tự "—" để tránh gây hiểu lầm cho học sinh.</t>
+          <t>Verify cac o grades chua co du lieu se display ky tu "—" de tranh gay hieu lam cho student.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học sinh này có một số cột điểm chưa được giáo viên nhập (ví dụ điểm thi lại TLCK hoặc điểm định kỳ ĐK3 đang trống trên Sheets).</t>
+          <t>Hoc sinh da log in. Hoc sinh nay co mot so cot grade chua duoc giao vien enter (e.g. grade thi lai TLCK hoac grade dinh ky DK3 dang trong tren Sheets).</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cập bảng điểm của học kỳ chứa môn Java Programming.
-2. Quan sát hiển thị tại cột thi lại "TLCK" và các ô điểm trống khác của môn học này.</t>
+          <t>1. Truy cap transcript cua semester chua mon Java Programming.
+2. Observe display tai cot thi lai "TLCK" va cac o grade trong khac cua course nay.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị ký tự "—" (gạch quang) tại các ô điểm chưa được nhập.
-Không hiển thị số "0" hoặc "0.0" hoặc để khoảng trống gây hiểu lầm, không xảy ra lỗi hiển thị hoặc lỗi hệ thống.</t>
+          <t>System display ky tu "—" (gach quang) tai cac o grade chua duoc enter.
+Khong display so "0" hoac "0.0" hoac de khoang trong gay hieu lam, khong xay ra error display hoac error system.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F03, Rule 7.5, Error Handling (Mục 9)</t>
+          <t>Related to M09-F03, Rule 7.5, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -1953,17 +1953,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Mã màu điểm tổng kết (/10) đạt loại Giỏi (&gt;= 8.0)</t>
+          <t>Ma mau grade tong ket (/10) dat loai Gioi (&gt;= 8.0)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Xác minh điểm tổng kết lớn hơn hoặc bằng 8.0 hiển thị màu Xanh lá (Green).</t>
+          <t>Verify grade tong ket lon hon hoac bang 8.0 display mau Xanh la (Green).</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập và đang xem bảng điểm học kỳ. Môn Math có điểm tổng kết là 8.0, môn IT Basics có điểm tổng kết là 9.2.</t>
+          <t>Hoc sinh da log in va dang xem transcript semester. Mon Math co grade tong ket la 8.0, mon IT Basics co grade tong ket la 9.2.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1973,13 +1973,13 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Tìm đến các môn Math và IT Basics trên bảng điểm.
-2. Quan sát màu sắc của điểm số hiển thị tại cột điểm tổng kết "/10".</t>
+          <t>1. Tim den cac mon Math va IT Basics tren transcript.
+2. Observe mau sac cua grades display tai cot grade tong ket "/10".</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Điểm số "8.0" và "9.2" hiển thị với màu xanh lá cây (Green) rõ ràng.</t>
+          <t>Diem so "8.0" va "9.2" display voi mau xanh la cay (Green) ro rang.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2022,17 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Mã màu điểm tổng kết (/10) đạt loại Khá/Trung bình (5.5 – 7.9)</t>
+          <t>Ma mau grade tong ket (/10) dat loai Kha/Trung binh (5.5 – 7.9)</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Xác minh điểm tổng kết từ 5.5 đến 7.9 hiển thị màu Cam (Orange).</t>
+          <t>Verify grade tong ket tu 5.5 den 7.9 display mau Cam (Orange).</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập và đang xem bảng điểm học kỳ. Môn English có điểm tổng kết là 5.5, môn Soft Skills có điểm tổng kết là 7.9.</t>
+          <t>Hoc sinh da log in va dang xem transcript semester. Mon English co grade tong ket la 5.5, mon Soft Skills co grade tong ket la 7.9.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -2042,13 +2042,13 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Tìm môn English và Soft Skills trên bảng điểm.
-2. Quan sát màu sắc hiển thị của điểm số tại cột điểm tổng kết "/10".</t>
+          <t>1. Tim mon English va Soft Skills tren transcript.
+2. Observe mau sac display cua grades tai cot grade tong ket "/10".</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Điểm số "5.5" và "7.9" hiển thị với màu cam (Orange) rõ ràng.</t>
+          <t>Diem so "5.5" va "7.9" display voi mau cam (Orange) ro rang.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -2091,17 +2091,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Mã màu điểm tổng kết (/10) loại Yếu (&lt; 5.5)</t>
+          <t>Ma mau grade tong ket (/10) loai Yeu (&lt; 5.5)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Xác minh điểm tổng kết nhỏ hơn 5.5 hiển thị màu Đỏ (Red).</t>
+          <t>Verify grade tong ket nho hon 5.5 display mau Do (Red).</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập và đang xem bảng điểm. Môn Web Development có điểm tổng kết là 5.4, môn Algorithms có điểm tổng kết là 4.0.</t>
+          <t>Hoc sinh da log in va dang xem transcript. Mon Web Development co grade tong ket la 5.4, mon Algorithms co grade tong ket la 4.0.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -2111,13 +2111,13 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Tìm môn Web Development và Algorithms trên bảng điểm.
-2. Quan sát màu sắc hiển thị của điểm số tại cột điểm tổng kết "/10".</t>
+          <t>1. Tim mon Web Development va Algorithms tren transcript.
+2. Observe mau sac display cua grades tai cot grade tong ket "/10".</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Điểm số "5.4" và "4.0" hiển thị với màu đỏ (Red) rõ ràng.</t>
+          <t>Diem so "5.4" va "4.0" display voi mau do (Red) ro rang.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>TC-M09-012</t>
@@ -2160,17 +2160,17 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Mã màu điểm GPA (/4) đạt loại Giỏi/Xuất sắc (&gt;= 3.5)</t>
+          <t>Ma mau grade GPA (/4) dat loai Gioi/Xuat sac (&gt;= 3.5)</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Xác minh điểm trung bình tích lũy học kỳ GPA lớn hơn hoặc bằng 3.5 hiển thị màu Xanh lá (Green).</t>
+          <t>Verify grade trung binh tich luy semester GPA lon hon hoac bang 3.5 display mau Xanh la (Green).</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học kỳ hiện tại học sinh đạt điểm trung bình GPA là 3.5 hoặc 3.8.</t>
+          <t>Hoc sinh da log in. Semester hien tai student dat grade trung binh GPA la 3.5 hoac 3.8.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -2180,13 +2180,13 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Quan sát vùng hiển thị điểm trung bình GPA học kỳ hiện tại trên giao diện.
-2. Kiểm tra màu sắc hiển thị của điểm GPA.</t>
+          <t>1. Observe vung display grade trung binh GPA semester hien tai tren interface.
+2. Verify mau sac display cua grade GPA.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Điểm số GPA "3.5" và "3.8" hiển thị với màu xanh lá cây (Green).</t>
+          <t>Diem so GPA "3.5" va "3.8" display voi mau xanh la cay (Green).</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -2229,17 +2229,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Mã màu điểm GPA (/4) đạt loại Trung bình/Khá (2.0 – 3.4)</t>
+          <t>Ma mau grade GPA (/4) dat loai Trung binh/Kha (2.0 – 3.4)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Xác minh điểm trung bình tích lũy học kỳ GPA từ 2.0 đến 3.4 hiển thị màu Cam (Orange).</t>
+          <t>Verify grade trung binh tich luy semester GPA tu 2.0 den 3.4 display mau Cam (Orange).</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học kỳ hiện tại học sinh đạt GPA là 2.0 hoặc 3.1.</t>
+          <t>Hoc sinh da log in. Semester hien tai student dat GPA la 2.0 hoac 3.1.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2249,13 +2249,13 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Quan sát khu vực hiển thị điểm trung bình GPA trên màn hình.
-2. Kiểm tra màu sắc hiển thị của điểm GPA.</t>
+          <t>1. Observe khu vuc display grade trung binh GPA tren man hinh.
+2. Verify mau sac display cua grade GPA.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Điểm GPA "2.0" và "3.1" hiển thị với màu cam (Orange).</t>
+          <t>Diem GPA "2.0" va "3.1" display voi mau cam (Orange).</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Mã màu điểm GPA (/4) loại Yếu (&lt; 2.0)</t>
+          <t>Ma mau grade GPA (/4) loai Yeu (&lt; 2.0)</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Xác minh điểm trung bình tích lũy học kỳ GPA nhỏ hơn 2.0 hiển thị màu Đỏ (Red).</t>
+          <t>Verify grade trung binh tich luy semester GPA nho hon 2.0 display mau Do (Red).</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Học kỳ hiện tại học sinh đạt GPA là 1.9 hoặc 1.2.</t>
+          <t>Hoc sinh da log in. Semester hien tai student dat GPA la 1.9 hoac 1.2.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2318,13 +2318,13 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Quan sát khu vực hiển thị điểm trung bình GPA trên màn hình.
-2. Kiểm tra màu sắc hiển thị của điểm GPA.</t>
+          <t>1. Observe khu vuc display grade trung binh GPA tren man hinh.
+2. Verify mau sac display cua grade GPA.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Điểm GPA "1.9" và "1.2" hiển thị với màu đỏ (Red).</t>
+          <t>Diem GPA "1.9" va "1.2" display voi mau do (Red).</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F04, Rule 5.5, Rule 7.6</t>
+          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
         </is>
       </c>
     </row>
@@ -2367,17 +2367,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Hiển thị nhãn Học lại (Re-study) cho môn học bị đánh dấu học lại</t>
+          <t>Hien thi nhan Hoc lai (Re-study) cho course bi danh dau hoc lai</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Xác minh môn học bị đánh dấu học lại trên hệ thống (Re-study = True) sẽ hiển thị nhãn cảnh báo màu đỏ.</t>
+          <t>Verify course bi danh dau hoc lai tren system (Re-study = True) se display nhan cphoto bao mau do.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập. Môn Database Management của học sinh này bị đánh dấu Re-study = True trên Sheets database. Môn Java Basics có Re-study = False.</t>
+          <t>Hoc sinh da log in. Mon Database Management cua student nay bi danh dau Re-study = True tren Sheets database. Mon Java Basics co Re-study = False.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cập bảng điểm học kỳ chứa môn Database Management và Java Basics.
-2. Kiểm tra cột "Re-study" hoặc phần nhãn bên cạnh tên mỗi môn học.</t>
+          <t>1. Truy cap transcript semester chua mon Database Management va Java Basics.
+2. Verify cot "Re-study" hoac phan nhan ben canh ten moi course.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Môn Database Management hiển thị một nhãn hoặc huy hiệu "Re-study" màu đỏ nổi bật.
-Môn Java Basics không hiển thị bất kỳ nhãn cảnh báo học lại nào.</t>
+          <t>Mon Database Management display mot nhan hoac huy hieu "Re-study" mau do noi bat.
+Mon Java Basics not displayed bat ky nhan cphoto bao hoc lai nao.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F05, Rule 7.7</t>
+          <t>Related to M09-F05, Rule 7.7</t>
         </is>
       </c>
     </row>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Hiển thị shortcut Báo cáo thực tập khi nhóm thực tập đang hoạt động (On-going)</t>
+          <t>Hien thi shortcut Bao cao internship khi internship group dang hoat dong (On-going)</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Xác minh shortcut dẫn đến Báo cáo thực tập hiển thị khi học sinh thuộc nhóm thực tập ở trạng thái On-going.</t>
+          <t>Verify shortcut dan den Bao cao internship display khi student thuoc internship group o status On-going.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Học sinh PNV26001 được phân bổ vào nhóm thực tập "Internship Group 2026". Trạng thái của nhóm thực tập này trong Sheet là "On-going".</t>
+          <t>Hoc sinh PNV26001 duoc phan bo vao internship group "Internship Group 2026". Status cua internship group nay trong Sheet la "On-going".</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -2457,15 +2457,15 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Đăng nhập tài khoản học sinh PNV26001.
-2. Quan sát giao diện Student Portal (khu vực thanh điều hướng hoặc bảng điều khiển).
-3. Xác minh sự xuất hiện của shortcut/nút "Bi-Weekly Internship Reports" (Báo cáo thực tập định kỳ).</t>
+          <t>1. Log in account student PNV26001.
+2. Observe interface Student Portal (khu vuc thanh dieu huong hoac bang dieu khien).
+3. Verify su xuat hien cua shortcut/nut "Bi-Weekly Internship Reports" (Bao cao internship dinh ky).</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Shortcut "Bi-Weekly Internship Reports" xuất hiện rõ ràng trên giao diện.
-Học sinh có thể nhấp vào để mở giao diện báo cáo thực tập.</t>
+          <t>Shortcut "Bi-Weekly Internship Reports" xuat hien ro rang tren interface.
+Hoc sinh can click vao de mo interface internship report.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F06, Rule 7.8</t>
+          <t>Related to M09-F06, Rule 7.8</t>
         </is>
       </c>
     </row>
@@ -2508,17 +2508,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Ẩn shortcut Báo cáo thực tập khi nhóm thực tập ở trạng thái khác On-going</t>
+          <t>An shortcut Bao cao internship khi internship group o status khac On-going</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Xác minh shortcut dẫn đến Báo cáo thực tập bị ẩn khi nhóm thực tập của học sinh ở trạng thái Planned hoặc Completed.</t>
+          <t>Verify shortcut dan den Bao cao internship bi an khi internship group cua student o status Planned hoac Completed.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Học sinh PNV26002 thuộc nhóm thực tập "Internship Group 2025" đã hoàn thành (trạng thái "Completed" trên hệ thống).</t>
+          <t>Hoc sinh PNV26002 thuoc internship group "Internship Group 2025" da hoan thanh (status "Completed" tren system).</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2528,15 +2528,15 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Đăng nhập tài khoản học sinh PNV26002.
-2. Quan sát giao diện Student Portal.
-3. Kiểm tra sự xuất hiện của nút/shortcut "Bi-Weekly Internship Reports".</t>
+          <t>1. Log in account student PNV26002.
+2. Observe interface Student Portal.
+3. Verify su xuat hien cua nut/shortcut "Bi-Weekly Internship Reports".</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Shortcut/nút liên kết đến Báo cáo thực tập hoàn toàn ẩn khỏi giao diện.
-Học sinh không thể nhìn thấy hay nhấp vào nút này.</t>
+          <t>Shortcut/nut lien ket den Bao cao internship hoan toan an khoi interface.
+Hoc sinh cannot nhin thay hay click button nay.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F06, Rule 7.8</t>
+          <t>Related to M09-F06, Rule 7.8</t>
         </is>
       </c>
     </row>
@@ -2579,17 +2579,17 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Ẩn shortcut Báo cáo thực tập khi học sinh chưa được phân bổ thực tập</t>
+          <t>An shortcut Bao cao internship khi student chua duoc phan bo internship</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Xác minh shortcut Báo cáo thực tập bị ẩn khi học sinh không thuộc bất kỳ nhóm thực tập nào.</t>
+          <t>Verify shortcut Bao cao internship bi an khi student khong thuoc bat ky internship group nao.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Học sinh PNV26003 chưa được gán vào bất kỳ nhóm thực tập nào trên Sheets cơ sở dữ liệu.</t>
+          <t>Hoc sinh PNV26003 chua duoc gan vao bat ky internship group nao tren Sheets co so du lieu.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -2599,14 +2599,14 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Đăng nhập tài khoản học sinh PNV26003.
-2. Quan sát giao diện Student Portal.
-3. Kiểm tra sự xuất hiện của nút/shortcut "Bi-Weekly Internship Reports".</t>
+          <t>1. Log in account student PNV26003.
+2. Observe interface Student Portal.
+3. Verify su xuat hien cua nut/shortcut "Bi-Weekly Internship Reports".</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Shortcut/nút liên kết đến Báo cáo thực tập ẩn hoàn toàn, không hiển thị trên giao diện của học sinh.</t>
+          <t>Shortcut/nut lien ket den Bao cao internship an hoan toan, not displayed tren interface cua student.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F06, Rule 7.8</t>
+          <t>Related to M09-F06, Rule 7.8</t>
         </is>
       </c>
     </row>
@@ -2649,17 +2649,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Xác minh cách ly dữ liệu giữa các học sinh (Data Isolation)</t>
+          <t>Verify cach ly du lieu giua cac student (Data Isolation)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Xác minh cơ chế bảo mật phía server đảm bảo học sinh chỉ xem được điểm của chính mình và bị từ chối truy cập dữ liệu của học sinh khác.</t>
+          <t>Verify co che bao mat phia server dam bao student chi xem duoc grade cua chinh minh va bi denies access du lieu cua student khac.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Học sinh PNV26001 và học sinh PNV26002 đều tồn tại trong hệ thống. Đã đăng nhập bằng tài khoản học sinh PNV26001.</t>
+          <t>Hoc sinh PNV26001 va student PNV26002 deu exist in system. Da log in bang account student PNV26001.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản student01@student.passerellesnumeriques.org.
-2. Tại giao diện bảng điểm, thử thay đổi tham số trên URL (ví dụ từ `?studentCode=PNV26001` thành `?studentCode=PNV26002`) hoặc dùng DevTools sửa mã request gửi về API backend để yêu cầu dữ liệu điểm của học sinh PNV26002.
-3. Quan sát kết quả hiển thị và phản hồi từ hệ thống.</t>
+          <t>1. Log in bang account student01@student.passerellesnumeriques.org.
+2. Tai interface transcript, thu thay doi tham so tren URL (e.g. tu `?studentCode=PNV26001` thanh `?studentCode=PNV26002`) hoac dung DevTools sua ma request gui ve API backend de requires du lieu grade cua student PNV26002.
+3. Observe ket qua display va phan hoi tu system.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối yêu cầu truy cập dữ liệu điểm của học sinh B.
-Màn hình không hiển thị điểm của học sinh B.
-Backend trả về thông báo lỗi phân quyền (ví dụ: "Unauthorized access" hoặc Access Denied).
-Bảng điểm hiển thị trên giao diện vẫn giữ nguyên của học sinh PNV26001 (hoặc hiển thị trang thông báo lỗi bảo mật).</t>
+          <t>System denies requires access du lieu grade cua student B.
+Man hinh not displayed grade cua student B.
+Backend tra ve notification error phan quyen (e.g.: "Unauthorized access" hoac Access Denied).
+Bang grade display tren interface van giu nguyen cua student PNV26001 (hoac display trang notification error bao mat).</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F07, Rule 7.9, Error Handling (Mục 9)</t>
+          <t>Related to M09-F07, Rule 7.9, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Chặn gọi API lấy điểm từ bên ngoài khi chưa xác thực</t>
+          <t>Chan goi API lay grade tu ben external khi chua xac thuc</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Xác minh các yêu cầu gọi API lấy điểm của học sinh gửi trực tiếp từ bên ngoài mà chưa qua đăng nhập Google OAuth đều bị từ chối.</t>
+          <t>Verify cac requires goi API lay grade cua student gui truc tiep tu ben external ma chua qua log in Google OAuth deu bi denies.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Người dùng chưa đăng nhập tài khoản. Trình duyệt ở chế độ ẩn danh hoặc sử dụng công cụ kiểm thử API (như Postman).</t>
+          <t>Nguoi dung chua log in account. Trinh duyet o che do an danh hoac su dung cong cu kiem thu API (nhu Postman).</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2742,16 +2742,16 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Mở cửa sổ ẩn danh hoặc công cụ kiểm thử API.
-2. Gửi request trực tiếp (HTTP GET/POST) đến URL API của hệ thống để lấy dữ liệu điểm của học sinh PNV26001.
-3. Quan sát phản hồi trả về từ hệ thống.</t>
+          <t>1. Mo cua so an danh hoac cong cu kiem thu API.
+2. Gui request truc tiep (HTTP GET/POST) den URL API cua system de lay du lieu grade cua student PNV26001.
+3. Observe phan hoi tra ve tu system.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Yêu cầu bị từ chối.
-Hệ thống phản hồi mã lỗi 401 Unauthorized (hoặc tương đương) hoặc chuyển hướng request về giao diện đăng nhập Google OAuth.
-Không có dữ liệu điểm nào được trả về.</t>
+          <t>Yeu cau bi denies.
+System phan hoi ma error 401 Unauthorized (hoac tuong duong) hoac redirect request ve interface log in Google OAuth.
+Khong co du lieu grade nao duoc tra ve.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M09-F07, Rule 7.9</t>
+          <t>Related to M09-F07, Rule 7.9</t>
         </is>
       </c>
     </row>
@@ -2794,17 +2794,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hiển thị giao diện trên thiết bị di động (Responsive UI)</t>
+          <t>Verify display interface tren thiet bi di dong (Responsive UI)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Xác minh giao diện Student Portal hiển thị tốt trên các thiết bị di động mà không bị vỡ khung hoặc mất thông tin điểm số.</t>
+          <t>Verify interface Student Portal display tot tren cac thiet bi di dong ma khong bi vo khung hoac mat thong tin grades.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công.</t>
+          <t>Hoc sinh da log in successfully.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>1. Đăng nhập Student Portal.
-2. Mở DevTools (F12) và kích hoạt chế độ Responsive Viewport giả lập màn hình iPhone X (375x812 px).
-3. Quan sát bộ chọn học kỳ, các danh mục và bảng điểm.
-4. Thao tác vuốt cuộn ngang bảng điểm để xem đầy đủ các cột điểm (KT TX, ĐK1-ĐK6, TCK, TLCK...).</t>
+          <t>1. Log in Student Portal.
+2. Mo DevTools (F12) va kich hoat che do Responsive Viewport gia lap man hinh iPhone X (375x812 px).
+3. Observe bo select semester, cac category va transcript.
+4. Thao tac vuot cuon ngang transcript de xem day du cac cot grade (KT TX, DK1-DK6, TCK, TLCK...).</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Giao diện tự động co giãn tương thích.
-Các tiêu đề danh mục và chữ hiển thị rõ ràng, không đè lên nhau.
-Bảng điểm hiển thị thanh cuộn ngang mượt mà cho phép xem hết các cột điểm mà không phá vỡ bố cục tổng thể của trang.</t>
+          <t>Interface tu dong co gian tuong thich.
+Cac tieu de category va chu display ro rang, khong de len nhau.
+Bang grade display thanh cuon ngang muot ma allows xem het cac cot grade ma khong pha vo bo cuc tong the cua trang.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Testing Environment (Mục 9)</t>
+          <t>Related to Testing Environment (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2867,17 +2867,17 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hành vi khi hết hạn phiên làm việc Google (Google Sign-Out)</t>
+          <t>Verify hanh vi khi het han phien lam viec Google (Google Sign-Out)</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống phát hiện phiên đăng nhập Google đã kết thúc và ngăn học sinh tiếp tục truy cập dữ liệu.</t>
+          <t>Dam bao system phat hien phien log in Google da ket thuc va ngan student tiep tuc access du lieu.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Học sinh đang đăng nhập và mở tab Student Portal.</t>
+          <t>Hoc sinh dang log in va mo tab Student Portal.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2887,17 +2887,17 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>1. Mở một tab trình duyệt khác, truy cập accounts.google.com và đăng xuất tài khoản Google hiện tại.
-2. Quay lại tab Student Portal.
-3. Thực hiện chuyển đổi học kỳ trên bộ chọn Semester Selector hoặc nhấn F5 để tải lại trang.
-4. Quan sát phản hồi của hệ thống.</t>
+          <t>1. Mo mot tab trinh duyet khac, access accounts.google.com va dang xuat account Google hien tai.
+2. Quay lai tab Student Portal.
+3. Thuc hien switching semester tren bo select Semester Selector hoac click F5 de tai lai trang.
+4. Observe phan hoi cua system.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống phát hiện phiên làm việc đã kết thúc.
-Các thao tác yêu cầu dữ liệu học kỳ mới bị dừng lại.
-Người dùng được chuyển hướng về trang đăng nhập Google OAuth hoặc hiển thị thông điệp yêu cầu đăng nhập lại để tiếp tục.</t>
+          <t>System phat hien phien lam viec da ket thuc.
+Cac thao tac requires du lieu semester moi bi dung lai.
+Nguoi dung duoc redirect ve trang log in Google OAuth hoac display thong diep requires log in lai de tiep tuc.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 7.1</t>
+          <t>Related to Rule 7.1</t>
         </is>
       </c>
     </row>
@@ -2940,17 +2940,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra xác thực tham số học kỳ không hợp lệ (Semester Validation)</t>
+          <t>Verify xac thuc tham so semester khong hop le (Semester Validation)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không bị lỗi crash và tự động xử lý an toàn khi tham số học kỳ được truyền vào không hợp lệ hoặc không tồn tại.</t>
+          <t>Verify system khong bi error crash va tu dong xu ly an toan khi tham so semester duoc truyen vao khong hop le hoac khong ton tai.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Học sinh đã đăng nhập thành công.</t>
+          <t>Hoc sinh da log in successfully.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2960,15 +2960,15 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1. Cố ý thay đổi tham số học kỳ trên đường dẫn URL thành giá trị không hợp lệ (ví dụ: `?semester=7` or `?semester=abc`).
-2. Tải lại trang hoặc cố tình gửi request với tham số không hợp lệ đó.
-3. Quan sát phản hồi của giao diện.</t>
+          <t>1. Co y thay doi tham so semester tren duong dan URL thanh gia tri khong hop le (e.g.: `?semester=7` or `?semester=abc`).
+2. Tai lai trang hoac co tinh gui request voi tham so khong hop le do.
+3. Observe phan hoi cua interface.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống không bị lỗi crash/trắng trang.
-Tự động quay về hiển thị dữ liệu của học kỳ mặc định (ví dụ: Học kỳ 1 hoặc học kỳ hiện tại hoạt động gần nhất), hoặc hiển thị thông báo lỗi "Học kỳ không hợp lệ".</t>
+          <t>System khong bi error crash/trang trang.
+Tu dong quay ve display du lieu cua semester mac dinh (e.g.: Semester 1 hoac semester hien tai hoat dong gan nhat), hoac display notification error "Semester khong hop le".</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8 - Semester)</t>
+          <t>Related to Validation Rules (Section 8 - Semester)</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module09_test_cases.xlsx
+++ b/Tests/excel/module09_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module09" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module09" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module09'!$A$1:$N$24</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,21 +429,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$16</f>
+              <f>'Report'!$A$9:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$C$9:$C$16</f>
+              <f>'Report'!$C$9:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -456,21 +456,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$16</f>
+              <f>'Report'!$A$9:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$D$9:$D$16</f>
+              <f>'Report'!$D$9:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -483,21 +483,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$16</f>
+              <f>'Report'!$A$9:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$E$9:$E$16</f>
+              <f>'Report'!$E$9:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -938,23 +938,23 @@
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="14">
-        <f>COUNTA(A9:A16)</f>
+        <f>COUNTA(A9:A18)</f>
         <v/>
       </c>
       <c r="B5" s="15">
-        <f>F17</f>
+        <f>F19</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIF(C9:C16, "&gt;0")</f>
+        <f>COUNTIF(C9:C18, "&gt;0")</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>COUNTIFS(C9:C16, 0, D9:D16, "&gt;0")</f>
+        <f>COUNTIFS(C9:C18, 0, D9:D18, "&gt;0")</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>COUNTIFS(C9:C16, 0, D9:D16, 0, E9:E16, "&gt;0")</f>
+        <f>COUNTIFS(C9:C18, 0, D9:D18, 0, E9:E18, "&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Read-only Academic View</t>
+          <t>Semester Navigation</t>
         </is>
       </c>
       <c r="C10" s="30">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Empty Grade Display</t>
+          <t>Subject Categorization</t>
         </is>
       </c>
       <c r="C11" s="24">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Read-only View Enforcement</t>
         </is>
       </c>
       <c r="C12" s="30">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Re-study Flag Display</t>
+          <t>Grade Representation &amp; Placeholders</t>
         </is>
       </c>
       <c r="C13" s="24">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Quick Access to Bi-Weekly Reports</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="C14" s="30">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Data Isolation</t>
+          <t>Re-study Status Display</t>
         </is>
       </c>
       <c r="C15" s="24">
@@ -1196,12 +1196,12 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>M09-UI</t>
+          <t>M09-F08</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>User Interface &amp; Responsiveness</t>
+          <t>Internship Report Shortcut Visibility</t>
         </is>
       </c>
       <c r="C16" s="30">
@@ -1221,30 +1221,86 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>M09-F09</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Student Data Isolation</t>
+        </is>
+      </c>
+      <c r="C17" s="24">
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$M$2:$M$24, "High")</f>
+        <v/>
+      </c>
+      <c r="D17" s="25">
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$M$2:$M$24, "Low")</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>SUM(C17:E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>M09-F10</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>Responsive Design</t>
+        </is>
+      </c>
+      <c r="C18" s="30">
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$M$2:$M$24, "High")</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$M$2:$M$24, "Low")</f>
+        <v/>
+      </c>
+      <c r="F18" s="33">
+        <f>SUM(C18:E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B17" s="35">
-        <f>COUNTA(A9:A16)&amp;" Features"</f>
-        <v/>
-      </c>
-      <c r="C17" s="34">
-        <f>SUM(C9:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="34">
-        <f>SUM(D9:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="34">
-        <f>SUM(E9:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="34">
-        <f>SUM(F9:F16)</f>
+      <c r="B19" s="35">
+        <f>COUNTA(A9:A18)&amp;" Features"</f>
+        <v/>
+      </c>
+      <c r="C19" s="34">
+        <f>SUM(C9:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="34">
+        <f>SUM(D9:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="34">
+        <f>SUM(E9:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="34">
+        <f>SUM(F9:F18)</f>
         <v/>
       </c>
     </row>
@@ -1351,7 +1407,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="135" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-M09-001</t>
@@ -1359,7 +1415,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1374,37 +1430,34 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Log in with a valid Student account</t>
+          <t>Log In with a Valid Student Account</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Verify student co email thuoc domain @student.passerellesnumeriques.org log in successfully vao Student Portal qua Google OAuth.</t>
+          <t>Verify student with email belonging to @student.passerellesnumeriques.org domain logs in successfully to Student Portal via Google OAuth.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung chua log in system. Trinh duyet da ket noi internet va ho tro Google OAuth.</t>
+          <t>User is not logged into system. Browser is connected to internet and supports Google OAuth.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>UserEmail=student01@student.passerellesnumeriques.org; Role=Student</t>
+          <t>Email="nam.nguyen26@student.passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cap URL cua system.
-2. Tai man hinh log in Google OAuth, enter account student01@student.passerellesnumeriques.org.
-3. Enter mat khau hop le va dong y cap quyen neu co.
-4. Observe trang web sau khi redirect.</t>
+          <t>1. Access Academic Portal login page;
+2. Click "Sign in with Google" button;
+3. Select account nam.nguyen26@student.passerellesnumeriques.org and authorize.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Log in successfully. Interface tu dong redirect den Student Portal (mac dinh mo tab Academic).
-Thong tin cua student display chinh xac bao gom Ho ten, Ma student o goc man hinh.
-Du lieu grade hoc tap cua chinh student nay duoc tai len successfully.</t>
+          <t>Login successful. System recognizes student role and redirects directly to Student Portal interface showing student's academic records.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1420,11 +1473,11 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F01, M09-F07, Rule 7.1, Rule 7.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="105" customHeight="1">
+          <t>Related Requirement: M09-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>TC-M09-002</t>
@@ -1432,7 +1485,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1447,36 +1500,34 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Log in with an organization Staff account</t>
+          <t>Log In with an Organization Staff Account</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Verify account Staff khi log in qua Google OAuth se duoc tu dong nhan dien domain va redirect den Staff Portal thay vi Student Portal.</t>
+          <t>Verify Staff account logging in via Google OAuth is automatically recognized and redirected to Staff Portal instead of Student Portal.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung chua log in system.</t>
+          <t>User is not logged into system.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>UserEmail=staff_user@passerellesnumeriques.org; Role=Staff</t>
+          <t>Email="staff.manager@passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cap URL cua system.
-2. Thuc hien log in qua Google OAuth bang account staff_user@passerellesnumeriques.org.
-3. Observe interface sau khi log in successfully.</t>
+          <t>1. Access Academic Portal login page;
+2. Click "Sign in with Google" button;
+3. Select Staff account staff.manager@passerellesnumeriques.org and authorize.</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Log in successfully.
-System tu dong nhan dien email thuoc domain @passerellesnumeriques.org.
-Chuyen huong user sang Staff Portal voi day du tinh nang quan tri. Khong display interface Student Portal.</t>
+          <t>Login successful. System recognizes Staff role and redirects user to Staff Portal interface instead of Student Portal.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1492,11 +1543,11 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F01, Rule 7.1, Docs - Section 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="105" customHeight="1">
+          <t>Related Requirement: M09-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-M09-003</t>
@@ -1504,7 +1555,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1519,36 +1570,34 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Log in with an external personal account</t>
+          <t>Log In with an External Personal Account</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Verify account email khong thuoc cac domain cua organization (e.g. @gmail.com) bi system chan access.</t>
+          <t>Verify system blocks access when user attempts to log in with an external personal email domain.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung chua log in system.</t>
+          <t>User is not logged into system.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>UserEmail=guest_user@gmail.com; Role=Guest</t>
+          <t>Email="user.test@gmail.com"</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cap URL cua system.
-2. Thuc hien log in qua Google OAuth bang account guest_user@gmail.com.
-3. Observe phan hoi cua system.</t>
+          <t>1. Access Academic Portal login page;
+2. Click "Sign in with Google" button;
+3. Select personal email user.test@gmail.com.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Log in failed.
-System denies quyen access cua email domain @gmail.com.
-Chuyen huong user sang trang bao error "Access Denied" (Tu choi access). Khong tai bat ky du lieu nao cua system.</t>
+          <t>System blocks login. Error message appears: "Access denied. Please use your organizational email (@passerellesnumeriques.org or @student.passerellesnumeriques.org)."</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1564,11 +1613,11 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F01, Rule 7.1, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="105" customHeight="1">
+          <t>Related Requirement: M09-F01, Error Handling 8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>TC-M09-004</t>
@@ -1576,7 +1625,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1591,36 +1640,32 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Log in with valid student email but without academic records in system</t>
+          <t>Log In with Valid Student Email but Without Academic Records in System</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Verify system khong bi error crash va display thong diep phu hop khi email student thuoc domain hop le nhung khong nam trong danh sach du lieu student.</t>
+          <t>Verify system handles student authentication when email domain is valid but student profile is missing from database.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung chua log in system. Tai khoan Google student ton tai nhung email nay chua duoc cau hinh trong Sheet danh sach student.</t>
+          <t>User has valid student email domain, but student profile record does not exist in database.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>UserEmail=new_student@student.passerellesnumeriques.org</t>
+          <t>Email="newstudent@student.passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cap URL cua system.
-2. Thuc hien log in qua Google OAuth bang account new_student@student.passerellesnumeriques.org.
-3. Observe interface sau khi redirect successfully.</t>
+          <t>1. Log in via Google OAuth with newstudent@student.passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Log in successfully vao Student Portal.
-System khong bi error crash/trang man hinh.
-Hien thi notification ro rang cho user: "No academic records found." (Khong tim thay du lieu hoc tap).</t>
+          <t>System authenticates but displays notice: "No academic records found for your account. Please contact Academic Staff."</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1629,18 +1674,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F01, M09-F07, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="180" customHeight="1">
+          <t>Related Requirement: M09-F01, Error Handling 8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-M09-005</t>
@@ -1648,7 +1693,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1658,44 +1703,39 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Read-only Academic View</t>
+          <t>Semester Navigation</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Switching between semesters (Semester Selector)</t>
+          <t>Switch Between Semesters (Semester Selector)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Verify tinh nang switching semester display dung du lieu grade cua semester duoc select.</t>
+          <t>Verify student can switch between semesters using dropdown menu and view corresponding subject grades and GPA.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in successfully vao Student Portal.
-Hoc sinh nay da co du lieu grade o nhieu semester (e.g.: Semester 1 va Semester 2).</t>
+          <t>Student is logged into Student Portal. Academic record contains data for Semester 1 and Semester 2.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; TargetSemester=Semester 2</t>
+          <t>Student Email="nam.nguyen26@student.passerellesnumeriques.org"; Selected Semester="Semester 2"</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Tai interface Student Portal, dinh vi bo select semester (Semester Selector).
-2. Nhap vao danh sach tha xuong va select "Semester 2" (Semester 2).
-3. Observe danh sach course va grades display.
-4. Nhap select lai "Semester 1" (Semester 1).
-5. Observe danh sach course va grades display.</t>
+          <t>1. Observe default selected semester (latest semester);
+2. Click Semester Selector dropdown menu;
+3. Select "Semester 2".</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Bang grade cap nhat nhanh chong va chinh xac theo semester duoc select.
-Khi select "Semester 2", system chi tai cac course va grades thuoc Semester 2.
-Khi select "Semester 1", system chi tai cac course va grades thuoc Semester 1.</t>
+          <t>Interface re-renders smoothly. Grade table and GPA stats update instantly to display Semester 2 academic data.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1711,11 +1751,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F02, Rule 7.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
+          <t>Related Requirement: M09-F02, Business Rules 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>TC-M09-006</t>
@@ -1723,52 +1763,48 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>M09-F02</t>
+          <t>M09-F03</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Read-only Academic View</t>
+          <t>Subject Categorization</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Verify categorization course theo category (Subject Categories)</t>
+          <t>Verify Subject Categorization by Category (Subject Categories)</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Verify cac course trong semester display dung categorization theo 4 category dao create.</t>
+          <t>Verify subjects on Student Portal are grouped into correct categories (IT, English, Professional Skills).</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in successfully vao Student Portal.
-Semester hien tai co chua cac course thuoc ca 4 category.</t>
+          <t>Student is logged into Student Portal. Student has enrolled subjects across multiple categories.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; SelectedSemester=Semester 1</t>
+          <t>Categories=["IT", "English", "Professional Skills"]</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Select Semester 1.
-2. Observe bo cuc display cua danh sach course.
-3. Verify whether cac course co duoc xep duoi cac tieu de group tuong ung hay khong: Fundamental, IT, English, Soft Skills.
-4. Doi chieu course cu the (e.g. mon Math phai thuoc Fundamental, Java thuoc IT).</t>
+          <t>1. Navigate to Grade Report tab on Student Portal;
+2. Observe layout of subject table.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Cac course duoc categorization chinh xac va display duoi cac tieu de category: Fundamental, IT, English, Soft Skills.
-Bo cuc categorization ro rang, de doc, khong co course nao bi xep sai group hoac khong co group.</t>
+          <t>Subjects are grouped clearly under Category header sections (IT, English, Professional Skills).</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1777,18 +1813,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F02, Rule 7.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="165" customHeight="1">
+          <t>Related Requirement: M09-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-M09-007</t>
@@ -1796,51 +1832,48 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>M09-F02</t>
+          <t>M09-F04</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Read-only Academic View</t>
+          <t>Read-only View Enforcement</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Verify tinh nang Read-only (Read-only) cua Student Portal</t>
+          <t>Verify Read-Only Nature of Student Portal</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Verify student hoan toan khong co quyen edit grades hay thuc hien cac tac vu thay doi du lieu tren interface.</t>
+          <t>Verify Student Portal is strictly Read-Only and provides no edit controls for grades or attendance.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in successfully vao Student Portal va dang o man hinh display grade.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001</t>
+          <t>Role="Student"</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Observe toan bo interface man hinh Academic.
-2. Verify su xuat hien cua cac nut: Edit (Edit), Save (Save), Delete (Delete), Enter grade (Import), Upload (Upload).
-3. Thu click chuot vao cac o grades (KT TX, DK1-DK6, TCK, TLCK, Final Score, GPA).
-4. Thu go ban phim de thay doi gia tri grade.</t>
+          <t>1. Browse all sections of Student Portal (Grades, Attendance, Profile, Materials);
+2. Check for any edit, save, or input fields.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Interface not displayed bat ky nut hoac cong cu nao allows edit, save, delete hoac enter du lieu.
-Tat ca grades display as van ban tinh (read-only), cannot click vao de edit hay enter lieu tu ban phim.</t>
+          <t>All academic data displays in Read-Only mode. No input fields or save buttons are present.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1856,11 +1889,11 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F02, Rule 7.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>Related Requirement: M09-F04, Business Rules 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>TC-M09-008</t>
@@ -1868,49 +1901,48 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>M09-F03</t>
+          <t>M09-F05</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Empty Grade Display</t>
+          <t>Grade Representation &amp; Placeholders</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Hien thi grades chua duoc enter (Empty Grades)</t>
+          <t>Display Unentered Grades (Empty Grades)</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Verify cac o grades chua co du lieu se display ky tu "—" de tranh gay hieu lam cho student.</t>
+          <t>Verify system displays hyphen placeholder "-" when a grade component has not been entered yet.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in. Hoc sinh nay co mot so cot grade chua duoc giao vien enter (e.g. grade thi lai TLCK hoac grade dinh ky DK3 dang trong tren Sheets).</t>
+          <t>Student is logged into Student Portal. Final Exam grade for subject "Web Dev" has not been entered by Staff.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; Subject=Java Programming; EmptyColumn=TLCK</t>
+          <t>Subject="Web Dev"; GradeComponent="Final Exam"</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cap transcript cua semester chua mon Java Programming.
-2. Observe display tai cot thi lai "TLCK" va cac o grade trong khac cua course nay.</t>
+          <t>1. View grade details for subject "Web Dev";
+2. Check cell display for Final Exam grade.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>System display ky tu "—" (gach quang) tai cac o grade chua duoc enter.
-Khong display so "0" hoac "0.0" hoac de khoang trong gay hieu lam, khong xay ra error display hoac error system.</t>
+          <t>Cell displays "-" placeholder instead of 0 or blank, indicating grade is pending.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1919,18 +1951,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F03, Rule 7.5, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1">
+          <t>Related Requirement: M09-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-M09-009</t>
@@ -1938,48 +1970,48 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Ma mau grade tong ket (/10) dat loai Gioi (&gt;= 8.0)</t>
+          <t>Color Code Final Grade (/10) for Excellent Grade (&gt;= 8.0)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Verify grade tong ket lon hon hoac bang 8.0 display mau Xanh la (Green).</t>
+          <t>Verify final subject grade &gt;= 8.0 displays in Green badge styling.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in va dang xem transcript semester. Mon Math co grade tong ket la 8.0, mon IT Basics co grade tong ket la 9.2.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; Subject1=Math; FinalScore1=8.0; Subject2=IT Basics; FinalScore2=9.2</t>
+          <t>Subject="Algorithms"; FinalGrade=8.5</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Tim den cac mon Math va IT Basics tren transcript.
-2. Observe mau sac cua grades display tai cot grade tong ket "/10".</t>
+          <t>1. Locate subject "Algorithms" with final grade 8.5;
+2. Inspect badge color.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Diem so "8.0" va "9.2" display voi mau xanh la cay (Green) ro rang.</t>
+          <t>Grade 8.5 displays in Green badge styling (#137333 / light green fill).</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1988,18 +2020,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Related Requirement: M09-F06, Color Rules 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>TC-M09-010</t>
@@ -2007,48 +2039,48 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Ma mau grade tong ket (/10) dat loai Kha/Trung binh (5.5 – 7.9)</t>
+          <t>Color Code Final Grade (/10) for Good/Average Grade (5.5 - 7.9)</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Verify grade tong ket tu 5.5 den 7.9 display mau Cam (Orange).</t>
+          <t>Verify final subject grade between 5.5 and 7.9 displays in Orange/Yellow badge styling.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in va dang xem transcript semester. Mon English co grade tong ket la 5.5, mon Soft Skills co grade tong ket la 7.9.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; Subject1=English; FinalScore1=5.5; Subject2=Soft Skills; FinalScore2=7.9</t>
+          <t>Subject="Database"; FinalGrade=6.5</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Tim mon English va Soft Skills tren transcript.
-2. Observe mau sac display cua grades tai cot grade tong ket "/10".</t>
+          <t>1. Locate subject "Database" with final grade 6.5;
+2. Inspect badge color.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Diem so "5.5" va "7.9" display voi mau cam (Orange) ro rang.</t>
+          <t>Grade 6.5 displays in Orange/Yellow badge styling (#B06000 / light yellow fill).</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2057,18 +2089,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
+          <t>Related Requirement: M09-F06, Color Rules 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-M09-011</t>
@@ -2076,48 +2108,48 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Ma mau grade tong ket (/10) loai Yeu (&lt; 5.5)</t>
+          <t>Color Code Final Grade (/10) for Failing Grade (&lt; 5.5)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Verify grade tong ket nho hon 5.5 display mau Do (Red).</t>
+          <t>Verify final subject grade &lt; 5.5 displays in Red badge styling.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in va dang xem transcript. Mon Web Development co grade tong ket la 5.4, mon Algorithms co grade tong ket la 4.0.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; Subject1=Web Development; FinalScore1=5.4; Subject2=Algorithms; FinalScore2=4.0</t>
+          <t>Subject="English 1"; FinalGrade=4.0</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Tim mon Web Development va Algorithms tren transcript.
-2. Observe mau sac display cua grades tai cot grade tong ket "/10".</t>
+          <t>1. Locate subject "English 1" with final grade 4.0;
+2. Inspect badge color.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Diem so "5.4" va "4.0" display voi mau do (Red) ro rang.</t>
+          <t>Grade 4.0 displays in Red badge styling (#A50E0E / light red fill).</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2126,18 +2158,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+          <t>Related Requirement: M09-F06, Color Rules 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>TC-M09-012</t>
@@ -2145,48 +2177,48 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Ma mau grade GPA (/4) dat loai Gioi/Xuat sac (&gt;= 3.5)</t>
+          <t>Color Code GPA (/4) for Excellent GPA (&gt;= 3.5)</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Verify grade trung binh tich luy semester GPA lon hon hoac bang 3.5 display mau Xanh la (Green).</t>
+          <t>Verify semester GPA &gt;= 3.5 displays in Green highlight styling.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in. Semester hien tai student dat grade trung binh GPA la 3.5 hoac 3.8.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; GPA=3.5; GPA2=3.8</t>
+          <t>GPA=3.65</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Observe vung display grade trung binh GPA semester hien tai tren interface.
-2. Verify mau sac display cua grade GPA.</t>
+          <t>1. View GPA Summary card on Student Portal;
+2. Inspect GPA badge color.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Diem so GPA "3.5" va "3.8" display voi mau xanh la cay (Green).</t>
+          <t>GPA 3.65 displays with Green text/background styling.</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2195,18 +2227,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Related Requirement: M09-F06, Color Rules 5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-M09-013</t>
@@ -2214,48 +2246,48 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Ma mau grade GPA (/4) dat loai Trung binh/Kha (2.0 – 3.4)</t>
+          <t>Color Code GPA (/4) for Good/Average GPA (2.0 - 3.4)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Verify grade trung binh tich luy semester GPA tu 2.0 den 3.4 display mau Cam (Orange).</t>
+          <t>Verify semester GPA between 2.0 and 3.4 displays in Orange/Yellow highlight styling.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in. Semester hien tai student dat GPA la 2.0 hoac 3.1.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; GPA=2.0; GPA2=3.1</t>
+          <t>GPA=2.85</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Observe khu vuc display grade trung binh GPA tren man hinh.
-2. Verify mau sac display cua grade GPA.</t>
+          <t>1. View GPA Summary card on Student Portal;
+2. Inspect GPA badge color.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Diem GPA "2.0" va "3.1" display voi mau cam (Orange).</t>
+          <t>GPA 2.85 displays with Orange/Yellow text/background styling.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2264,18 +2296,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>Related Requirement: M09-F06, Color Rules 5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TC-M09-014</t>
@@ -2283,48 +2315,48 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>M09-F04</t>
+          <t>M09-F06</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Score Color Coding</t>
+          <t>Grade Color Coding</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Ma mau grade GPA (/4) loai Yeu (&lt; 2.0)</t>
+          <t>Color Code GPA (/4) for Low GPA (&lt; 2.0)</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Verify grade trung binh tich luy semester GPA nho hon 2.0 display mau Do (Red).</t>
+          <t>Verify semester GPA &lt; 2.0 displays in Red highlight styling.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in. Semester hien tai student dat GPA la 1.9 hoac 1.2.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; GPA=1.9; GPA2=1.2</t>
+          <t>GPA=1.75</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Observe khu vuc display grade trung binh GPA tren man hinh.
-2. Verify mau sac display cua grade GPA.</t>
+          <t>1. View GPA Summary card on Student Portal;
+2. Inspect GPA badge color.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Diem GPA "1.9" va "1.2" display voi mau do (Red).</t>
+          <t>GPA 1.75 displays with Red text/background styling.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2333,18 +2365,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F04, Rule 5.5, Rule 7.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="75" customHeight="1">
+          <t>Related Requirement: M09-F06, Color Rules 5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-M09-015</t>
@@ -2352,49 +2384,48 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>M09-F05</t>
+          <t>M09-F07</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Re-study Flag Display</t>
+          <t>Re-study Status Display</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Hien thi nhan Hoc lai (Re-study) cho course bi danh dau hoc lai</t>
+          <t>Display Retake/Re-study Badge for Retaken Course</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Verify course bi danh dau hoc lai tren system (Re-study = True) se display nhan cphoto bao mau do.</t>
+          <t>Verify system displays a clear "Re-study" or "Retake" badge next to subjects flagged for re-study.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in. Mon Database Management cua student nay bi danh dau Re-study = True tren Sheets database. Mon Java Basics co Re-study = False.</t>
+          <t>Student is logged into Student Portal. Subject "Networking" is flagged as Re-study.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; Subject1=Database Management; ReStudy1=True; Subject2=Java Basics; ReStudy2=False</t>
+          <t>Subject="Networking"; IsRestudy=True</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cap transcript semester chua mon Database Management va Java Basics.
-2. Verify cot "Re-study" hoac phan nhan ben canh ten moi course.</t>
+          <t>1. View subject list for current semester;
+2. Inspect row for subject "Networking".</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Mon Database Management display mot nhan hoac huy hieu "Re-study" mau do noi bat.
-Mon Java Basics not displayed bat ky nhan cphoto bao hoc lai nao.</t>
+          <t>Subject row displays a prominent "Re-study" badge next to course name.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2410,11 +2441,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F05, Rule 7.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="120" customHeight="1">
+          <t>Related Requirement: M09-F07, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M09-016</t>
@@ -2422,50 +2453,48 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>M09-F06</t>
+          <t>M09-F08</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Quick Access to Bi-Weekly Reports</t>
+          <t>Internship Report Shortcut Visibility</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Hien thi shortcut Bao cao internship khi internship group dang hoat dong (On-going)</t>
+          <t>Display Internship Report Shortcut when Internship Group Is Active (On-going)</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Verify shortcut dan den Bao cao internship display khi student thuoc internship group o status On-going.</t>
+          <t>Verify system displays Internship Report shortcut button on Student Portal header when student belongs to an active internship group.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh PNV26001 duoc phan bo vao internship group "Internship Group 2026". Status cua internship group nay trong Sheet la "On-going".</t>
+          <t>Student is logged into Student Portal. Student belongs to an internship group with status "On-going".</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; InternshipGroup=Internship Group 2026; Status=On-going</t>
+          <t>InternshipGroupStatus="On-going"</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Log in account student PNV26001.
-2. Observe interface Student Portal (khu vuc thanh dieu huong hoac bang dieu khien).
-3. Verify su xuat hien cua shortcut/nut "Bi-Weekly Internship Reports" (Bao cao internship dinh ky).</t>
+          <t>1. Open Student Portal home page;
+2. Check header navigation bar.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Shortcut "Bi-Weekly Internship Reports" xuat hien ro rang tren interface.
-Hoc sinh can click vao de mo interface internship report.</t>
+          <t>Internship Report shortcut button is visible and clicking it opens bi-weekly report submission module.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2481,11 +2510,11 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F06, Rule 7.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1">
+          <t>Related Requirement: M09-F08, Business Rules 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-M09-017</t>
@@ -2493,50 +2522,48 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>M09-F06</t>
+          <t>M09-F08</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Quick Access to Bi-Weekly Reports</t>
+          <t>Internship Report Shortcut Visibility</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>An shortcut Bao cao internship khi internship group o status khac On-going</t>
+          <t>Hide Internship Report Shortcut when Internship Group Status Is Not On-going</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Verify shortcut dan den Bao cao internship bi an khi internship group cua student o status Planned hoac Completed.</t>
+          <t>Verify system hides Internship Report shortcut button when internship group status is Completed or Archived.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh PNV26002 thuoc internship group "Internship Group 2025" da hoan thanh (status "Completed" tren system).</t>
+          <t>Student is logged into Student Portal. Student belongs to an internship group with status "Completed".</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26002; InternshipGroup=Internship Group 2025; Status=Completed</t>
+          <t>InternshipGroupStatus="Completed"</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Log in account student PNV26002.
-2. Observe interface Student Portal.
-3. Verify su xuat hien cua nut/shortcut "Bi-Weekly Internship Reports".</t>
+          <t>1. Open Student Portal home page;
+2. Check header navigation bar.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Shortcut/nut lien ket den Bao cao internship hoan toan an khoi interface.
-Hoc sinh cannot nhin thay hay click button nay.</t>
+          <t>Internship Report shortcut button is hidden from header.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2552,11 +2579,11 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F06, Rule 7.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
+          <t>Related Requirement: M09-F08, Business Rules 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TC-M09-018</t>
@@ -2564,49 +2591,48 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>M09-F06</t>
+          <t>M09-F08</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Quick Access to Bi-Weekly Reports</t>
+          <t>Internship Report Shortcut Visibility</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>An shortcut Bao cao internship khi student chua duoc phan bo internship</t>
+          <t>Hide Internship Report Shortcut when Student Is Not Assigned to Any Internship Group</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Verify shortcut Bao cao internship bi an khi student khong thuoc bat ky internship group nao.</t>
+          <t>Verify system hides Internship Report shortcut button when student has not been assigned to any internship group.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh PNV26003 chua duoc gan vao bat ky internship group nao tren Sheets co so du lieu.</t>
+          <t>Student is logged into Student Portal. Student is not in any internship group.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26003; InternshipGroup=None</t>
+          <t>InternshipGroup=None</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Log in account student PNV26003.
-2. Observe interface Student Portal.
-3. Verify su xuat hien cua nut/shortcut "Bi-Weekly Internship Reports".</t>
+          <t>1. Open Student Portal home page;
+2. Check header navigation bar.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Shortcut/nut lien ket den Bao cao internship an hoan toan, not displayed tren interface cua student.</t>
+          <t>Internship Report shortcut button is completely hidden from header.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2622,11 +2648,11 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F06, Rule 7.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="165" customHeight="1">
+          <t>Related Requirement: M09-F08, Business Rules 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-M09-019</t>
@@ -2634,52 +2660,49 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>M09-F07</t>
+          <t>M09-F09</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Data Isolation</t>
+          <t>Student Data Isolation</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Verify cach ly du lieu giua cac student (Data Isolation)</t>
+          <t>Verify Data Isolation Between Students (Data Isolation)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Verify co che bao mat phia server dam bao student chi xem duoc grade cua chinh minh va bi denies access du lieu cua student khac.</t>
+          <t>Verify student can only view their own grades and cannot access academic records of other students.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh PNV26001 va student PNV26002 deu exist in system. Da log in bang account student PNV26001.</t>
+          <t>Student A (ST001) is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>AuthEmail=student01@student.passerellesnumeriques.org; TargetStudentCode=PNV26002</t>
+          <t>StudentA_ID="ST001"; StudentB_ID="ST002"</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Log in bang account student01@student.passerellesnumeriques.org.
-2. Tai interface transcript, thu thay doi tham so tren URL (e.g. tu `?studentCode=PNV26001` thanh `?studentCode=PNV26002`) hoac dung DevTools sua ma request gui ve API backend de requires du lieu grade cua student PNV26002.
-3. Observe ket qua display va phan hoi tu system.</t>
+          <t>1. Log in as Student A;
+2. Inspect displayed student name, ID, and grades;
+3. Attempt to alter URL parameters to request Student B (ST002) record.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>System denies requires access du lieu grade cua student B.
-Man hinh not displayed grade cua student B.
-Backend tra ve notification error phan quyen (e.g.: "Unauthorized access" hoac Access Denied).
-Bang grade display tren interface van giu nguyen cua student PNV26001 (hoac display trang notification error bao mat).</t>
+          <t>Student A sees strictly ST001 records. Attempting to tamper URL parameters returns 403 Forbidden or redirects to own profile.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2695,11 +2718,11 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Related to M09-F07, Rule 7.9, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="105" customHeight="1">
+          <t>Related Requirement: M09-F09, Security Standards 7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>TC-M09-020</t>
@@ -2707,51 +2730,47 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>M09-F07</t>
+          <t>M09-F09</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Data Isolation</t>
+          <t>Student Data Isolation</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Chan goi API lay grade tu ben external khi chua xac thuc</t>
+          <t>Block Direct API Calls for Unauthenticated Grade Retrieval</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Verify cac requires goi API lay grade cua student gui truc tiep tu ben external ma chua qua log in Google OAuth deu bi denies.</t>
+          <t>Verify backend grade fetch API rejects requests lacking valid session JWT token.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung chua log in account. Trinh duyet o che do an danh hoac su dung cong cu kiem thu API (nhu Postman).</t>
+          <t>Unauthenticated user.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>TargetApiUrl=https://script.google.com/macros/s/.../exec?action=getGrades&amp;studentCode=PNV26001</t>
+          <t>ApiEndpoint="GET /api/student/grades"</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Mo cua so an danh hoac cong cu kiem thu API.
-2. Gui request truc tiep (HTTP GET/POST) den URL API cua system de lay du lieu grade cua student PNV26001.
-3. Observe phan hoi tra ve tu system.</t>
+          <t>1. Submit direct HTTP GET request to grade API without Authorization header.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Yeu cau bi denies.
-System phan hoi ma error 401 Unauthorized (hoac tuong duong) hoac redirect request ve interface log in Google OAuth.
-Khong co du lieu grade nao duoc tra ve.</t>
+          <t>Backend rejects request with HTTP 401 Unauthorized.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2767,11 +2786,11 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Related to M09-F07, Rule 7.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="165" customHeight="1">
+          <t>Related Requirement: M09-F09, Security Standards 7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TC-M09-021</t>
@@ -2779,52 +2798,48 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>M09-UI</t>
+          <t>M09-F10</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>User Interface &amp; Responsiveness</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Verify display interface tren thiet bi di dong (Responsive UI)</t>
+          <t>Verify Interface Rendering on Mobile Devices (Responsive UI)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Verify interface Student Portal display tot tren cac thiet bi di dong ma khong bi vo khung hoac mat thong tin grades.</t>
+          <t>Verify Student Portal layout adapts cleanly to small screen viewports (smartphones/tablets).</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in successfully.</t>
+          <t>Student is logged into Student Portal. Browser viewport set to 375px width (iPhone dimensions).</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>ViewportSize=375x812 (iPhone X)</t>
+          <t>ViewportWidth="375px"</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>1. Log in Student Portal.
-2. Mo DevTools (F12) va kich hoat che do Responsive Viewport gia lap man hinh iPhone X (375x812 px).
-3. Observe bo select semester, cac category va transcript.
-4. Thao tac vuot cuon ngang transcript de xem day du cac cot grade (KT TX, DK1-DK6, TCK, TLCK...).</t>
+          <t>1. Resize viewport to 375px width;
+2. Inspect grade table, cards, navigation bar, and buttons.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Interface tu dong co gian tuong thich.
-Cac tieu de category va chu display ro rang, khong de len nhau.
-Bang grade display thanh cuon ngang muot ma allows xem het cac cot grade ma khong pha vo bo cuc tong the cua trang.</t>
+          <t>Layout stacks vertically without horizontal scroll overflow. Table scrolls smoothly or collapses into cards cleanly.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2840,11 +2855,11 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Related to Testing Environment (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="150" customHeight="1">
+          <t>Related Requirement: M09-F10, UI Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>TC-M09-022</t>
@@ -2852,7 +2867,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2867,37 +2882,32 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Verify hanh vi khi het han phien lam viec Google (Google Sign-Out)</t>
+          <t>Verify Behavior when Session Expires (Google Sign-Out / Session Expiry)</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Dam bao system phat hien phien log in Google da ket thuc va ngan student tiep tuc access du lieu.</t>
+          <t>Verify system redirects student to login page when session token expires.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh dang log in va mo tab Student Portal.</t>
+          <t>Student session token has expired after period of inactivity.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Action=Google Sign-Out</t>
+          <t>SessionState="Expired"</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>1. Mo mot tab trinh duyet khac, access accounts.google.com va dang xuat account Google hien tai.
-2. Quay lai tab Student Portal.
-3. Thuc hien switching semester tren bo select Semester Selector hoac click F5 de tai lai trang.
-4. Observe phan hoi cua system.</t>
+          <t>1. Perform action on Student Portal after session expiration.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>System phat hien phien lam viec da ket thuc.
-Cac thao tac requires du lieu semester moi bi dung lai.
-Nguoi dung duoc redirect ve trang log in Google OAuth hoac display thong diep requires log in lai de tiep tuc.</t>
+          <t>System clears session state, displays notification "Session expired. Please sign in again", and redirects to login page.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -2913,11 +2923,11 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 7.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="120" customHeight="1">
+          <t>Related Requirement: M09-F01, Security Standards 7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TC-M09-023</t>
@@ -2925,7 +2935,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Module 09 – Student Portal</t>
+          <t>Module 09 - Student Portal</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2935,40 +2945,37 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Read-only Academic View</t>
+          <t>Semester Navigation</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Verify xac thuc tham so semester khong hop le (Semester Validation)</t>
+          <t>Verify Validation of Invalid Semester Parameter (Semester Validation)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Verify system khong bi error crash va tu dong xu ly an toan khi tham so semester duoc truyen vao khong hop le hoac khong ton tai.</t>
+          <t>Verify system handles invalid or non-existent semester parameters in URL gracefully.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh da log in successfully.</t>
+          <t>Student is logged into Student Portal.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>InvalidSemester=Semester 7; InvalidSemester2=abc</t>
+          <t>InvalidSemesterParam="semester=999"</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1. Co y thay doi tham so semester tren duong dan URL thanh gia tri khong hop le (e.g.: `?semester=7` or `?semester=abc`).
-2. Tai lai trang hoac co tinh gui request voi tham so khong hop le do.
-3. Observe phan hoi cua interface.</t>
+          <t>1. Navigate to Student Portal URL with parameter semester=999.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>System khong bi error crash/trang trang.
-Tu dong quay ve display du lieu cua semester mac dinh (e.g.: Semester 1 hoac semester hien tai hoat dong gan nhat), hoac display notification error "Semester khong hop le".</t>
+          <t>System defaults to current active semester without crashing or throwing unhandled exception.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -2984,7 +2991,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8 - Semester)</t>
+          <t>Related Requirement: M09-F02, Error Handling 8.3</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module09_test_cases.xlsx
+++ b/Tests/excel/module09_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module09" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module09" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module09'!$A$1:$N$24</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module09_test_cases.xlsx
+++ b/Tests/excel/module09_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module09" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module09'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module09'!$A$1:$O$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1009,15 +1009,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A9, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A9, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A9, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A9, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A9, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A9, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1037,15 +1037,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A10, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A10, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A10, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A10, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A10, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A10, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1065,15 +1065,15 @@
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A11, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A11, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A11, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A11, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A11, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A11, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1093,15 +1093,15 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A12, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A12, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A12, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A12, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A12, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A12, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1121,15 +1121,15 @@
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A13, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A13, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A13, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A13, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A13, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A13, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1149,15 +1149,15 @@
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A14, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A14, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A14, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A14, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A14, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A14, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A15, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A15, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A15, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A15, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A15, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A15, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1205,15 +1205,15 @@
         </is>
       </c>
       <c r="C16" s="30">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A16, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A16, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D16" s="31">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A16, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A16, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A16, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A16, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="33">
@@ -1233,15 +1233,15 @@
         </is>
       </c>
       <c r="C17" s="24">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A17, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1261,15 +1261,15 @@
         </is>
       </c>
       <c r="C18" s="30">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$M$2:$M$24, "High")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$N$2:$N$24, "High")</f>
         <v/>
       </c>
       <c r="D18" s="31">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$M$2:$M$24, "Medium")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$N$2:$N$24, "Medium")</f>
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$M$2:$M$24, "Low")</f>
+        <f>COUNTIFS('Module09'!$C$2:$C$24, A18, 'Module09'!$N$2:$N$24, "Low")</f>
         <v/>
       </c>
       <c r="F18" s="33">
@@ -1316,7 +1316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1331,8 +1331,9 @@
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1398,10 +1399,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1466,12 +1472,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F01, Business Rules 6.1</t>
         </is>
@@ -1536,12 +1543,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F01, Business Rules 6.1</t>
         </is>
@@ -1606,12 +1614,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F01, Error Handling 8.1</t>
         </is>
@@ -1674,12 +1683,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F01, Error Handling 8.2</t>
         </is>
@@ -1744,12 +1754,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F02, Business Rules 6.2</t>
         </is>
@@ -1813,12 +1824,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F03, Business Rules 6.3</t>
         </is>
@@ -1882,12 +1894,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F04, Business Rules 6.4</t>
         </is>
@@ -1951,12 +1964,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F05, Business Rules 6.5</t>
         </is>
@@ -2020,12 +2034,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F06, Color Rules 5.1</t>
         </is>
@@ -2089,12 +2104,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F06, Color Rules 5.1</t>
         </is>
@@ -2158,12 +2174,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F06, Color Rules 5.1</t>
         </is>
@@ -2227,12 +2244,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F06, Color Rules 5.2</t>
         </is>
@@ -2296,12 +2314,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F06, Color Rules 5.2</t>
         </is>
@@ -2365,12 +2384,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F06, Color Rules 5.2</t>
         </is>
@@ -2434,12 +2454,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F07, Business Rules 6.7</t>
         </is>
@@ -2503,12 +2524,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F08, Business Rules 6.8</t>
         </is>
@@ -2572,12 +2594,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F08, Business Rules 6.8</t>
         </is>
@@ -2641,12 +2664,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F08, Business Rules 6.8</t>
         </is>
@@ -2711,12 +2735,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F09, Security Standards 7.1</t>
         </is>
@@ -2779,12 +2804,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F09, Security Standards 7.1</t>
         </is>
@@ -2848,12 +2874,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F10, UI Standards</t>
         </is>
@@ -2916,12 +2943,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F01, Security Standards 7.2</t>
         </is>
@@ -2984,24 +3012,25 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M09-F02, Error Handling 8.3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N24"/>
+  <autoFilter ref="A1:O24"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="N2:N124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tests/excel/module09_test_cases.xlsx
+++ b/Tests/excel/module09_test_cases.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="239">
   <si>
     <t>Module 09 - Feature &amp; Priority Summary Report</t>
   </si>
@@ -691,6 +691,75 @@
   </si>
   <si>
     <t>Passed</t>
+  </si>
+  <si>
+    <t>Login was successful. The system recognized the Student role and redirected the user to the Student Portal displaying the student's academic records.</t>
+  </si>
+  <si>
+    <t>Login was successful. The system recognized the Staff role and redirected the user to the Staff Portal instead of the Student Portal.</t>
+  </si>
+  <si>
+    <t>The system correctly blocked login using an external personal email address and displayed the appropriate access denied message.</t>
+  </si>
+  <si>
+    <t>The system authenticated the user successfully and displayed the message informing that no academic records were found for the account.</t>
+  </si>
+  <si>
+    <t>The selected semester was loaded successfully. The grade table and GPA summary were updated correctly according to the selected semester.</t>
+  </si>
+  <si>
+    <t>All subjects were grouped correctly under their respective categories (IT, English, and Professional Skills).</t>
+  </si>
+  <si>
+    <t>All academic information was displayed in read-only mode. No edit, save, or input controls were available.</t>
+  </si>
+  <si>
+    <t>The system displayed the "-" placeholder correctly for the unentered grade component.</t>
+  </si>
+  <si>
+    <t>The final grade (8.5) was displayed with the correct green badge styling.</t>
+  </si>
+  <si>
+    <t>The final grade (6.5) was displayed with the correct orange/yellow badge styling.</t>
+  </si>
+  <si>
+    <t>The final grade (4.0) was displayed with the correct red badge styling.</t>
+  </si>
+  <si>
+    <t>The GPA (3.65) was displayed with the correct green highlight styling.</t>
+  </si>
+  <si>
+    <t>The GPA (2.85) was displayed with the correct orange/yellow highlight styling.</t>
+  </si>
+  <si>
+    <t>The GPA (1.75) was displayed with the correct red highlight styling.</t>
+  </si>
+  <si>
+    <t>The "Re-study" badge was displayed correctly next to the retaken subject.</t>
+  </si>
+  <si>
+    <t>The Internship Report shortcut button was displayed on the header and successfully opened the bi-weekly report submission module.</t>
+  </si>
+  <si>
+    <t>The Internship Report shortcut button was hidden when the internship group status was Completed.</t>
+  </si>
+  <si>
+    <t>The Internship Report shortcut button was not displayed because the student was not assigned to any internship group.</t>
+  </si>
+  <si>
+    <t>The logged-in student could only access their own academic records. Attempts to access another student's data were blocked with HTTP 403 or redirected to the student's own profile.</t>
+  </si>
+  <si>
+    <t>The backend rejected the unauthenticated API request and returned HTTP 401 Unauthorized.</t>
+  </si>
+  <si>
+    <t>The interface adapted correctly to the mobile viewport. All components displayed properly without horizontal overflow.</t>
+  </si>
+  <si>
+    <t>After the session expired, the system cleared the session, displayed the session expiration notification, and redirected the user to the login page.</t>
+  </si>
+  <si>
+    <t>The system handled the invalid semester parameter correctly by loading the current active semester without any errors or unexpected behavior.</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1109,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="1"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1440,7 +1508,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1478,7 +1545,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1492,7 +1558,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="1"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2273,7 +2338,9 @@
       <c r="J2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="L2" s="5" t="s">
         <v>215</v>
       </c>
@@ -2316,7 +2383,9 @@
       <c r="J3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="9"/>
+      <c r="K3" s="9" t="s">
+        <v>217</v>
+      </c>
       <c r="L3" s="5" t="s">
         <v>215</v>
       </c>
@@ -2359,7 +2428,9 @@
       <c r="J4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>218</v>
+      </c>
       <c r="L4" s="5" t="s">
         <v>215</v>
       </c>
@@ -2371,7 +2442,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>72</v>
       </c>
@@ -2402,7 +2473,9 @@
       <c r="J5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="9" t="s">
+        <v>219</v>
+      </c>
       <c r="L5" s="5" t="s">
         <v>215</v>
       </c>
@@ -2445,7 +2518,9 @@
       <c r="J6" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4" t="s">
+        <v>220</v>
+      </c>
       <c r="L6" s="5" t="s">
         <v>215</v>
       </c>
@@ -2488,7 +2563,9 @@
       <c r="J7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K7" s="9"/>
+      <c r="K7" s="9" t="s">
+        <v>221</v>
+      </c>
       <c r="L7" s="5" t="s">
         <v>215</v>
       </c>
@@ -2531,7 +2608,9 @@
       <c r="J8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="4" t="s">
+        <v>222</v>
+      </c>
       <c r="L8" s="5" t="s">
         <v>215</v>
       </c>
@@ -2574,7 +2653,9 @@
       <c r="J9" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="9" t="s">
+        <v>223</v>
+      </c>
       <c r="L9" s="5" t="s">
         <v>215</v>
       </c>
@@ -2617,7 +2698,9 @@
       <c r="J10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="L10" s="5" t="s">
         <v>215</v>
       </c>
@@ -2660,7 +2743,9 @@
       <c r="J11" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="K11" s="9"/>
+      <c r="K11" s="9" t="s">
+        <v>225</v>
+      </c>
       <c r="L11" s="5" t="s">
         <v>215</v>
       </c>
@@ -2703,7 +2788,9 @@
       <c r="J12" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="L12" s="5" t="s">
         <v>215</v>
       </c>
@@ -2746,7 +2833,9 @@
       <c r="J13" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="K13" s="9"/>
+      <c r="K13" s="9" t="s">
+        <v>227</v>
+      </c>
       <c r="L13" s="5" t="s">
         <v>215</v>
       </c>
@@ -2789,7 +2878,9 @@
       <c r="J14" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="4" t="s">
+        <v>228</v>
+      </c>
       <c r="L14" s="5" t="s">
         <v>215</v>
       </c>
@@ -2832,7 +2923,9 @@
       <c r="J15" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="K15" s="9"/>
+      <c r="K15" s="9" t="s">
+        <v>229</v>
+      </c>
       <c r="L15" s="5" t="s">
         <v>215</v>
       </c>
@@ -2875,7 +2968,9 @@
       <c r="J16" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="K16" s="4"/>
+      <c r="K16" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="L16" s="5" t="s">
         <v>215</v>
       </c>
@@ -2918,7 +3013,9 @@
       <c r="J17" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="9" t="s">
+        <v>231</v>
+      </c>
       <c r="L17" s="5" t="s">
         <v>215</v>
       </c>
@@ -2961,7 +3058,9 @@
       <c r="J18" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="K18" s="4"/>
+      <c r="K18" s="4" t="s">
+        <v>232</v>
+      </c>
       <c r="L18" s="5" t="s">
         <v>215</v>
       </c>
@@ -3004,7 +3103,9 @@
       <c r="J19" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="K19" s="9"/>
+      <c r="K19" s="9" t="s">
+        <v>233</v>
+      </c>
       <c r="L19" s="5" t="s">
         <v>215</v>
       </c>
@@ -3047,7 +3148,9 @@
       <c r="J20" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="K20" s="4"/>
+      <c r="K20" s="4" t="s">
+        <v>234</v>
+      </c>
       <c r="L20" s="5" t="s">
         <v>215</v>
       </c>
@@ -3090,7 +3193,9 @@
       <c r="J21" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="K21" s="9"/>
+      <c r="K21" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="L21" s="5" t="s">
         <v>215</v>
       </c>
@@ -3133,7 +3238,9 @@
       <c r="J22" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="K22" s="4"/>
+      <c r="K22" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="L22" s="5" t="s">
         <v>215</v>
       </c>
@@ -3176,7 +3283,9 @@
       <c r="J23" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K23" s="9"/>
+      <c r="K23" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="L23" s="5" t="s">
         <v>215</v>
       </c>
@@ -3219,7 +3328,9 @@
       <c r="J24" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="K24" s="4"/>
+      <c r="K24" s="4" t="s">
+        <v>238</v>
+      </c>
       <c r="L24" s="5" t="s">
         <v>215</v>
       </c>
